--- a/data/trans_dic/P2A_ner_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2A_ner_R-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental</t>
+          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,22; 12,7</t>
+          <t>2,2; 12,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,05; 17,5</t>
+          <t>2,97; 16,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,71; 18,0</t>
+          <t>3,43; 17,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,52; 15,77</t>
+          <t>2,65; 14,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,44</t>
+          <t>0,0; 3,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,76</t>
+          <t>0,0; 7,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,92; 16,17</t>
+          <t>3,74; 17,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,63; 11,05</t>
+          <t>3,62; 11,17</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,65</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 10,01</t>
+          <t>2,03; 9,93</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,9; 14,04</t>
+          <t>5,13; 14,38</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,09</t>
+          <t>0,79; 2,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,19; 5,97</t>
+          <t>2,24; 5,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,86; 7,71</t>
+          <t>3,79; 7,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,39; 8,14</t>
+          <t>4,48; 8,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,29</t>
+          <t>0,96; 3,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,16</t>
+          <t>0,8; 3,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,43; 7,1</t>
+          <t>3,38; 7,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,78; 8,69</t>
+          <t>4,87; 9,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,59</t>
+          <t>1,04; 2,69</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,83</t>
+          <t>1,71; 3,8</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,15; 6,92</t>
+          <t>4,05; 6,8</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,22; 8,2</t>
+          <t>5,1; 7,87</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 5,08</t>
+          <t>0,62; 5,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,24</t>
+          <t>0,64; 5,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,73</t>
+          <t>0,99; 5,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,65</t>
+          <t>0,5; 3,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 7,03</t>
+          <t>1,21; 6,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,6</t>
+          <t>0,0; 3,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 8,61</t>
+          <t>2,18; 8,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 5,82</t>
+          <t>0,91; 5,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,86</t>
+          <t>1,29; 4,75</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,42</t>
+          <t>0,57; 3,63</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 5,86</t>
+          <t>2,02; 6,26</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,65</t>
+          <t>1,03; 3,7</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,38</t>
+          <t>1,35; 3,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,54</t>
+          <t>1,89; 4,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,68; 6,75</t>
+          <t>3,57; 6,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,92; 7,1</t>
+          <t>4,04; 6,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,11</t>
+          <t>1,7; 4,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,39</t>
+          <t>0,75; 2,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,51; 6,42</t>
+          <t>3,42; 6,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,33; 7,53</t>
+          <t>4,34; 7,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,77; 3,31</t>
+          <t>1,74; 3,33</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,05</t>
+          <t>1,44; 2,96</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,95; 6,05</t>
+          <t>3,9; 6,01</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,59; 6,74</t>
+          <t>4,57; 6,7</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3198</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3325</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4713</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3997</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1298</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>5482</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>7195</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4623</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>10194</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1240; 6891</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1205; 6803</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1875; 9611</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1359; 7656</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2206</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3980</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2317; 10650</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>3906; 12041</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2176</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>1867; 9121</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>5980; 16781</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>5078</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11301</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>19148</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>28910</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>6509</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5576</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>19247</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>33920</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>11587</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>16876</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>38395</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>62831</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2441; 9187</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>6830; 17561</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>13207; 27394</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>20635; 38853</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>3389; 11530</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2711; 10218</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>12828; 26942</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>25162; 46626</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>6885; 17882</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>10996; 24520</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>29536; 49509</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>49819; 76945</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2723</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2884</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3816</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2439</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>3943</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1396</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>6542</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>4453</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>6666</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4280</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>10358</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>6891</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>850; 6938</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>750; 6721</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1346; 7694</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>747; 5819</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1496; 8368</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5066</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>3049; 12126</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1669; 9805</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>3358; 12367</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1442; 9202</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5579; 17268</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3418; 12306</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>11000</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>14185</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>26289</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>36061</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>14449</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>7400</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>27087</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>43855</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>25448</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>21585</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>53375</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>79916</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>6795; 17334</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>9022; 21847</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>18735; 35273</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>26859; 46468</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>8985; 21348</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>4017; 13079</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>19518; 36715</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>33070; 55711</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>17985; 34398</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>14645; 30019</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>42709; 65880</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>65200; 95537</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P2A_ner_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2A_ner_R-Estudios-trans_dic.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,2; 12,2</t>
+          <t>2,18; 12,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -727,52 +727,52 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,97; 16,74</t>
+          <t>3,03; 17,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,43; 17,58</t>
+          <t>3,01; 16,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,65; 14,9</t>
+          <t>3,64; 16,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,55</t>
+          <t>0,0; 3,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,77</t>
+          <t>0,0; 8,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,74; 17,18</t>
+          <t>4,28; 17,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,62; 11,17</t>
+          <t>3,37; 11,47</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>0,0; 1,84</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 9,93</t>
+          <t>2,11; 9,76</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,13; 14,38</t>
+          <t>4,91; 13,8</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,96</t>
+          <t>0,79; 3,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,24; 5,76</t>
+          <t>2,31; 5,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,79; 7,86</t>
+          <t>3,72; 7,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,48; 8,44</t>
+          <t>4,42; 8,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,26</t>
+          <t>0,91; 3,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,01</t>
+          <t>0,73; 3,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,38; 7,09</t>
+          <t>3,58; 7,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,87; 9,03</t>
+          <t>4,81; 8,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,69</t>
+          <t>1,07; 2,72</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 3,8</t>
+          <t>1,72; 3,9</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,05; 6,8</t>
+          <t>4,0; 6,71</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,1; 7,87</t>
+          <t>5,04; 7,99</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 5,08</t>
+          <t>0,62; 5,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,75</t>
+          <t>0,65; 6,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 5,66</t>
+          <t>0,97; 5,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 3,89</t>
+          <t>0,47; 3,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 6,77</t>
+          <t>1,14; 6,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,7</t>
+          <t>0,0; 3,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 8,67</t>
+          <t>2,33; 8,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,35</t>
+          <t>0,83; 5,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,75</t>
+          <t>1,17; 4,52</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,63</t>
+          <t>0,57; 3,61</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 6,26</t>
+          <t>2,11; 6,22</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,7</t>
+          <t>1,16; 3,87</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,44</t>
+          <t>1,25; 3,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,58</t>
+          <t>1,84; 4,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,57; 6,71</t>
+          <t>3,72; 6,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,04; 6,99</t>
+          <t>4,03; 7,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,04</t>
+          <t>1,74; 3,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,43</t>
+          <t>0,73; 2,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,42; 6,43</t>
+          <t>3,5; 6,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,34; 7,31</t>
+          <t>4,41; 7,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,33</t>
+          <t>1,76; 3,39</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,96</t>
+          <t>1,43; 2,96</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,9; 6,01</t>
+          <t>3,79; 5,99</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,57; 6,7</t>
+          <t>4,61; 6,76</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1240; 6891</t>
+          <t>1232; 7135</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1514,52 +1514,52 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1205; 6803</t>
+          <t>1233; 7231</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1875; 9611</t>
+          <t>1645; 9188</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1359; 7656</t>
+          <t>1869; 8371</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2206</t>
+          <t>0; 2419</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3980</t>
+          <t>0; 4288</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2317; 10650</t>
+          <t>2655; 10686</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3906; 12041</t>
+          <t>3636; 12363</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 2176</t>
+          <t>0; 2168</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1867; 9121</t>
+          <t>1941; 8963</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5980; 16781</t>
+          <t>5731; 16102</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2441; 9187</t>
+          <t>2437; 9710</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6830; 17561</t>
+          <t>7043; 18237</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13207; 27394</t>
+          <t>12962; 27485</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20635; 38853</t>
+          <t>20357; 39291</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3389; 11530</t>
+          <t>3222; 11598</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2711; 10218</t>
+          <t>2479; 11071</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12828; 26942</t>
+          <t>13602; 27316</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25162; 46626</t>
+          <t>24875; 45772</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6885; 17882</t>
+          <t>7115; 18064</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10996; 24520</t>
+          <t>11113; 25143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29536; 49509</t>
+          <t>29108; 48854</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>49819; 76945</t>
+          <t>49217; 78032</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>850; 6938</t>
+          <t>851; 7126</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>750; 6721</t>
+          <t>754; 7611</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1346; 7694</t>
+          <t>1318; 7713</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>747; 5819</t>
+          <t>697; 5579</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1496; 8368</t>
+          <t>1407; 8312</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5066</t>
+          <t>0; 4838</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3049; 12126</t>
+          <t>3255; 12317</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1669; 9805</t>
+          <t>1526; 9642</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3358; 12367</t>
+          <t>3053; 11768</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1442; 9202</t>
+          <t>1444; 9158</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5579; 17268</t>
+          <t>5827; 17158</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3418; 12306</t>
+          <t>3873; 12893</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6795; 17334</t>
+          <t>6303; 17237</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9022; 21847</t>
+          <t>8788; 22044</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18735; 35273</t>
+          <t>19551; 35676</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26859; 46468</t>
+          <t>26767; 46786</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8985; 21348</t>
+          <t>9182; 20637</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4017; 13079</t>
+          <t>3953; 12722</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19518; 36715</t>
+          <t>19984; 37235</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>33070; 55711</t>
+          <t>33568; 56348</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17985; 34398</t>
+          <t>18112; 34993</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14645; 30019</t>
+          <t>14501; 30036</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>42709; 65880</t>
+          <t>41585; 65626</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>65200; 95537</t>
+          <t>65836; 96455</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_ner_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2A_ner_R-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7,78%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9,48%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>5,66%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>8,18%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8,62%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,78%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 12,64</t>
+          <t>3,52; 15,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 3,44</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 8,76</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4,42; 17,84</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2,22; 12,7</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3,03; 17,79</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3,01; 16,8</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3,64; 16,3</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,9</t>
-        </is>
-      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,37</t>
+          <t>3,05; 17,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,28; 17,23</t>
+          <t>4,39; 19,96</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,37; 11,47</t>
+          <t>3,63; 11,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,84</t>
+          <t>0,0; 1,65</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,11; 9,76</t>
+          <t>2,02; 10,01</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,91; 13,8</t>
+          <t>5,57; 15,64</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>1,64%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5,07%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6,98%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>3,71%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>5,49%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6,28%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>5,07%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,13</t>
+          <t>0,94; 3,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,31; 5,99</t>
+          <t>0,78; 3,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,72; 7,88</t>
+          <t>3,43; 7,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,42; 8,53</t>
+          <t>5,04; 9,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,28</t>
+          <t>0,8; 3,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,26</t>
+          <t>2,19; 5,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,58; 7,19</t>
+          <t>3,86; 7,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,81; 8,86</t>
+          <t>4,95; 8,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,72</t>
+          <t>1,0; 2,59</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,9</t>
+          <t>1,69; 3,83</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,0; 6,71</t>
+          <t>4,15; 6,92</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,04; 7,99</t>
+          <t>5,68; 8,85</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1,99%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2,47%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2,81%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 5,22</t>
+          <t>1,17; 7,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,51</t>
+          <t>0,0; 3,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 5,67</t>
+          <t>2,07; 8,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,73</t>
+          <t>0,93; 4,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 6,73</t>
+          <t>0,49; 5,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,53</t>
+          <t>0,65; 6,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,33; 8,8</t>
+          <t>0,95; 5,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 5,26</t>
+          <t>0,52; 3,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,52</t>
+          <t>1,31; 4,86</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,61</t>
+          <t>0,6; 3,42</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,11; 6,22</t>
+          <t>2,1; 5,86</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,87</t>
+          <t>0,93; 3,42</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6,04%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>2,19%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,97%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>5,0%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,42%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,42</t>
+          <t>1,76; 4,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,62</t>
+          <t>0,67; 2,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,72; 6,79</t>
+          <t>3,51; 6,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,03; 7,04</t>
+          <t>4,49; 7,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,9</t>
+          <t>1,37; 3,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,36</t>
+          <t>1,93; 4,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,5; 6,52</t>
+          <t>3,68; 6,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,41; 7,39</t>
+          <t>4,37; 7,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 3,39</t>
+          <t>1,77; 3,31</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,96</t>
+          <t>1,52; 3,05</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,79; 5,99</t>
+          <t>3,95; 6,05</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,61; 6,76</t>
+          <t>4,91; 7,14</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,54 +1436,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3997</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1298</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5379</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>3198</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>3325</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4713</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3997</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>4752</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>7195</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>429</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1298</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>5482</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>7195</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>429</t>
-        </is>
-      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
           <t>4623</t>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10194</t>
+          <t>10131</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1232; 7135</t>
+          <t>1811; 8102</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>0; 2135</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4490</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2508; 10119</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1254; 7168</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1233; 7231</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1645; 9188</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1869; 8371</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0; 2419</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4288</t>
+          <t>1238; 7110</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2655; 10686</t>
+          <t>2052; 9332</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3636; 12363</t>
+          <t>3914; 11917</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 2168</t>
+          <t>0; 1937</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1941; 8963</t>
+          <t>1858; 9200</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5731; 16102</t>
+          <t>5759; 16181</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>43</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6509</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5576</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>19247</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>33192</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>5078</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>11301</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>19148</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>28910</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6509</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5576</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>19247</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>33920</t>
+          <t>29944</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>62831</t>
+          <t>63136</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2437; 9710</t>
+          <t>3315; 11644</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7043; 18237</t>
+          <t>2661; 10737</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12962; 27485</t>
+          <t>13012; 26982</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20357; 39291</t>
+          <t>23981; 44212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3222; 11598</t>
+          <t>2483; 9579</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2479; 11071</t>
+          <t>6680; 18189</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13602; 27316</t>
+          <t>13469; 26895</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24875; 45772</t>
+          <t>21424; 38650</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7115; 18064</t>
+          <t>6667; 17205</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11113; 25143</t>
+          <t>10912; 24690</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29108; 48854</t>
+          <t>30232; 50415</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>49217; 78032</t>
+          <t>51604; 80338</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>3943</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1396</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6542</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3757</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>2723</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>2884</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>3816</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2439</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>3943</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1396</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>6542</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4453</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6891</t>
+          <t>6379</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>851; 7126</t>
+          <t>1444; 8690</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>754; 7611</t>
+          <t>0; 4923</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1318; 7713</t>
+          <t>2892; 12049</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>697; 5579</t>
+          <t>1566; 8337</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1407; 8312</t>
+          <t>674; 6934</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4838</t>
+          <t>761; 7291</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3255; 12317</t>
+          <t>1289; 7793</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1526; 9642</t>
+          <t>782; 5800</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3053; 11768</t>
+          <t>3414; 12646</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1444; 9158</t>
+          <t>1510; 8684</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5827; 17158</t>
+          <t>5806; 16181</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3873; 12893</t>
+          <t>2974; 10891</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>55</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>14449</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7400</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>27087</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>42328</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>11000</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>14185</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>26289</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>36061</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>14449</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7400</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>27087</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>43855</t>
+          <t>37319</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>79916</t>
+          <t>79646</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6303; 17237</t>
+          <t>9318; 21718</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8788; 22044</t>
+          <t>3583; 12897</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19551; 35676</t>
+          <t>20042; 36656</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26767; 46786</t>
+          <t>31498; 55840</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9182; 20637</t>
+          <t>6875; 17028</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3953; 12722</t>
+          <t>9196; 21670</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19984; 37235</t>
+          <t>19342; 35472</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>33568; 56348</t>
+          <t>27497; 47225</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18112; 34993</t>
+          <t>18219; 34190</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14501; 30036</t>
+          <t>15435; 30955</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>41585; 65626</t>
+          <t>43336; 66358</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>65836; 96455</t>
+          <t>65267; 94991</t>
         </is>
       </c>
     </row>
